--- a/artfynd/A 62848-2019 artfynd.xlsx
+++ b/artfynd/A 62848-2019 artfynd.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ward Tamsyn, Tore Dahlberg</t>
+          <t>Tore Dahlberg, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 62848-2019 artfynd.xlsx
+++ b/artfynd/A 62848-2019 artfynd.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Ward Tamsyn</t>
+          <t>Ward Tamsyn, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
